--- a/04_DESIGN_TABLES/DesignTable_1504_SW2.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_1504_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN4"/>
+  <dimension ref="A1:BN7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1186,218 +1186,878 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1504-20-20-FG</t>
+          <t>1504-08-08-FG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9375</v>
+        <v>0.531</v>
       </c>
       <c r="D4" t="n">
-        <v>1.04</v>
+        <v>0.76</v>
       </c>
       <c r="E4" t="n">
-        <v>0.695</v>
+        <v>0.304</v>
       </c>
       <c r="F4" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.3795</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.4425</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="U4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
-        <v>0.9048</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.08253</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.7775</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.819</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0.8141</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0.768</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.6405</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.875</v>
-      </c>
       <c r="V4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="n">
-        <v>1.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>0.9375</v>
+        <v>0.531</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.01</v>
+        <v>0.46</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.48</v>
+        <v>0.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.555</v>
+        <v>0.759</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5385</v>
+        <v>0.388</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.7775</v>
+        <v>0.3795</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.84707</v>
+        <v>0.43664</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.77</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.48</v>
+        <v>0.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.16</v>
+        <v>0.75</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.08696</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.74</v>
+        <v>0.35</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.80957</v>
+        <v>0.40714</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>1.875</v>
+        <v>1.062</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.73</v>
+        <v>0.54</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.875</v>
+        <v>1.062</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.18</v>
+        <v>0.68</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.9375</v>
+        <v>0.531</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.9375</v>
+        <v>0.531</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.54077</v>
+        <v>0.30607</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.54077</v>
+        <v>0.30607</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.08203</v>
+        <v>0.61265</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.73</v>
+        <v>0.54</v>
       </c>
       <c r="AY4" t="n">
         <v>0.04</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.6</v>
+        <v>0.267</v>
       </c>
       <c r="BA4" t="n">
-        <v>1.6238</v>
+        <v>0.91972</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.73</v>
+        <v>0.54</v>
       </c>
       <c r="BC4" t="n">
         <v>0.04</v>
       </c>
       <c r="BD4" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>1504-08-08-FG</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>45 deg Female Pipe x Female NPSM Swivel Elbow, 1/2-14 NPSM (female swivel) x 1/2-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>1/2-14 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>1/2-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N2 / M / W2 / nut hex / flats / stem bore from the Brennan TFA catalog p.22; tap drill, thread majors from the end library | 2026-10-20 (batch 19 D_geom): DataStatus MISSING -&gt; ASSUMED - one source (Brennan TFA catalog p.22 TFA-p022-t01); generated with the batch-17 1504 SPEC; D@BORE = Brennan A2 DRILL - flag: OMi's 2026-10-18 drawings of sibling 1504 sizes print the stem bore 0.01-0.02 below the Brennan drill on 7 of 7 bores (wave2 tee_elbow), so the true bore may be slightly smaller | PORTDEPTH 0.75 = Brennan port depth -08 = 0.750 (Brennan 1502 / 2505 / 2606 / 5502 / 5504 / 5505 / 5603 / 5605 / 5652 -08 STEPs and 5 more) (brennan_port_depths_out.txt) - Q-ANGLED-P1 settled from the Brennan STEPs 2026-10-18 (the MS51503 P1 library value does not fit the 45 deg female leg) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W2 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); NPSM swivel neck turned clear of the forged corner as on 6502 (NECKTRIM1 revolve cut + NECKFILL1 ring back to the neck, in every configuration; no change where the corner stays inside the neck): Brennan 1503-08-08-FG / 1503-12-08-FG / 1504-06-06-FG STEPs (tools/measure/neck45.py 2026-10-18): body face 0.400 / 0.570 / 0.360 inside the hex corner radius 0.5052 / 0.6131 / 0.5052, neck 0.304 / 0.304 / 0.2465, nothing outside the neck from the body face to the nut rear face (excess 0.000) - ASSUMED for every NPSM size (Q-ANGLED-NECKNPSM, settled from the Brennan STEPs 2026-10-18); past the swivel slot start the corner must lie inside the stem by 0.02 (slot test on what the corner reaches, N2); female NPTF port on the 45 deg leg (Q-NEW-ANGLEDFEMALE): the 5504 / 1502 forged female leg turned to the 135 deg axis - hex arm to 0.26 short of the port face, round collar of dia = the hex flats, tap drill from the port face (pocket), tapered helical thread over the port depth (Brennan 1504-06-06-FG / 5505-08-08-FG / 5503-16-16-FG STEPs: collar 0.26 at the flats dia on the 45 deg leg, the same end as on the axis legs); helical thread on the 45 deg leg (HelixThreadV, 2026-10-18): helix on the leg end face (circle centred on the leg axis), started in the Front Plane, right hand, into the part, tapered as on the axis legs; 60deg tooth profile on the Front Plane with its sides parallel / normal to the leg axis, swept along the helix - the thread of the axis legs (HelixThread) about the 135 deg axis; SolidWorks' Thread feature is not used there (an off-axis Thread feature crashed SolidWorks 2026-10-15); drawing-only thread, suppressed in the saved model and STEP; leg 2 port depth 0.750 = the row PORTDEPTH instead of MS51503 P1 0.9 (which does not fit the 0.94 leg): the port depth Brennan draws for -08: 0.750 (Brennan 1502 / 2505 / 2606 / 5502 / 5504 / 5505 / 5603 / 5605 / 5652 -08 STEPs and 5 more); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: tap drill = the row's TAPDRILL (end library: the per-size tap drill every built female pipe port carries, Q-TRANSFER-ENDLIB = yes 2026-10-08), tapered helix over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - where that does not fit the short 45 deg leg (P1 &gt;= leg - 0.05) over the row's PORTDEPTH = the port depth Brennan draws for that size (Q-ANGLED-P1, settled from the Brennan STEPs 2026-10-18; said per leg below); connecting drill to the axis crossing = the tap drill carried to the crossing (Brennan 1504-06-06-FG / 5503-16-16-FG / 5505-08-08-FG STEPs, OCP 2026-10-18: the drill runs from the bottom of the tapered port to the axis crossing and ends flat there; the other leg bore opens into it); the 1.79deg port cone and the 45deg mouth chamfer are NOT modelled; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.22 alone, end details from the end library; marked DimSource BRENNAN | 2026-10-20: DataStatus MISSING -&gt; ASSUMED (Brennan catalog only; 1504 / 6807 SPEC exists since batch 17) | leg 1: the corner puck (radius 0.613) reaches 0.073 past the swivel body face (0.540) but stays inside the neck (max 0.290 off the axis vs neck radius 0.304) - as on the Brennan 6502-08-08-FG / 1503-08-08-FG forgings</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>1504-08-08-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1504-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5694</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.7216900000000001</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.6189</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.4635</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.485</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.54214</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.455</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.51214</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.787</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.75698</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>1.13623</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>1504-12-12-FG</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>45 deg Female Pipe x Female NPSM Swivel Elbow, 3/4-14 NPSM (female swivel) x 3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>3/4-14 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>3/4-14 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N2 / M / W2 / nut hex / flats / stem bore from the Brennan TFA catalog p.22; tap drill, thread majors from the end library | 2026-10-20 (batch 19 D_geom): DataStatus MISSING -&gt; ASSUMED - one source (Brennan TFA catalog p.22 TFA-p022-t01); generated with the batch-17 1504 SPEC; D@BORE = Brennan A2 DRILL - flag: OMi's 2026-10-18 drawings of sibling 1504 sizes print the stem bore 0.01-0.02 below the Brennan drill on 7 of 7 bores (wave2 tee_elbow), so the true bore may be slightly smaller | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W2 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); NPSM swivel neck turned clear of the forged corner as on 6502 (NECKTRIM1 revolve cut + NECKFILL1 ring back to the neck, in every configuration; no change where the corner stays inside the neck): Brennan 1503-08-08-FG / 1503-12-08-FG / 1504-06-06-FG STEPs (tools/measure/neck45.py 2026-10-18): body face 0.400 / 0.570 / 0.360 inside the hex corner radius 0.5052 / 0.6131 / 0.5052, neck 0.304 / 0.304 / 0.2465, nothing outside the neck from the body face to the nut rear face (excess 0.000) - ASSUMED for every NPSM size (Q-ANGLED-NECKNPSM, settled from the Brennan STEPs 2026-10-18); past the swivel slot start the corner must lie inside the stem by 0.02 (slot test on what the corner reaches, N2); female NPTF port on the 45 deg leg (Q-NEW-ANGLEDFEMALE): the 5504 / 1502 forged female leg turned to the 135 deg axis - hex arm to 0.26 short of the port face, round collar of dia = the hex flats, tap drill from the port face (pocket), tapered helical thread over the port depth (Brennan 1504-06-06-FG / 5505-08-08-FG / 5503-16-16-FG STEPs: collar 0.26 at the flats dia on the 45 deg leg, the same end as on the axis legs); helical thread on the 45 deg leg (HelixThreadV, 2026-10-18): helix on the leg end face (circle centred on the leg axis), started in the Front Plane, right hand, into the part, tapered as on the axis legs; 60deg tooth profile on the Front Plane with its sides parallel / normal to the leg axis, swept along the helix - the thread of the axis legs (HelixThread) about the 135 deg axis; SolidWorks' Thread feature is not used there (an off-axis Thread feature crashed SolidWorks 2026-10-15); drawing-only thread, suppressed in the saved model and STEP; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: tap drill = the row's TAPDRILL (end library: the per-size tap drill every built female pipe port carries, Q-TRANSFER-ENDLIB = yes 2026-10-08), tapered helix over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - where that does not fit the short 45 deg leg (P1 &gt;= leg - 0.05) over the row's PORTDEPTH = the port depth Brennan draws for that size (Q-ANGLED-P1, settled from the Brennan STEPs 2026-10-18; said per leg below); connecting drill to the axis crossing = the tap drill carried to the crossing (Brennan 1504-06-06-FG / 5503-16-16-FG / 5505-08-08-FG STEPs, OCP 2026-10-18: the drill runs from the bottom of the tapered port to the axis crossing and ends flat there; the other leg bore opens into it); the 1.79deg port cone and the 45deg mouth chamfer are NOT modelled; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.22 alone, end details from the end library; marked DimSource BRENNAN | 2026-10-20: DataStatus MISSING -&gt; ASSUMED (Brennan catalog only; 1504 / 6807 SPEC exists since batch 17) | leg 2: female port thread length = MS51503 P1 0.91 (library) - the row has no measured PORTDEPTH@BORE; leg 1: the corner (radius 0.757) reaches past the swivel slot start (0.741) but stays inside the stem there (worst margin 0.3068 at 0.7411: corner 0.1567 off the axis vs 0.4635) - hidden in solid (slot test N2, 2026-10-18); leg 1: the corner (puck radius 0.757) stands 0.121 out of the neck past the swivel body face (0.560; 0.510 off the axis vs neck radius 0.389) - turned down to the neck from the body face to the nut rear face (0.615) by NECKTRIM1 / NECKFILL1, as on the Brennan 6502-12-12-FG STEP (NECK-6502, 2026-10-01)</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>1504-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1504-16-16-FG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7098</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.86603</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.6465</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.7447</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.4845</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1.211</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.469</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.6055</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.6750699999999999</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.63957</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.93769</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.40729</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>1504-16-16-FG</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>45 deg Female Pipe x Female NPSM Swivel Elbow, 1-11 1/2 NPSM (female swivel) x 1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPSM (female swivel)</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>1-11 1/2 NPTF (female)</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU dropped by the 2026-09-23 crawl (adapters77, 2026-10-16); NO Air-Way row for this size; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): N2 / M / W2 / nut hex / flats / stem bore from the Brennan TFA catalog p.22; tap drill, thread majors from the end library | 2026-10-20 (batch 19 D_geom): DataStatus MISSING -&gt; ASSUMED - one source (Brennan TFA catalog p.22 TFA-p022-t01); generated with the batch-17 1504 SPEC; D@BORE = Brennan A2 DRILL - flag: OMi's 2026-10-18 drawings of sibling 1504 sizes print the stem bore 0.01-0.02 below the Brennan drill on 7 of 7 bores (wave2 tee_elbow), so the true bore may be slightly smaller | PORTDEPTH 0.94 = Brennan port depth -16 = 0.940 (Brennan 5405-16-16, 5502-16-16-FG, 5503-16-16-FG STEPs) (brennan_port_depths_out.txt) - Q-ANGLED-P1 settled from the Brennan STEPs 2026-10-18 (the MS51503 P1 library value does not fit the 45 deg female leg) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W2 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); NPSM swivel neck turned clear of the forged corner as on 6502 (NECKTRIM1 revolve cut + NECKFILL1 ring back to the neck, in every configuration; no change where the corner stays inside the neck): Brennan 1503-08-08-FG / 1503-12-08-FG / 1504-06-06-FG STEPs (tools/measure/neck45.py 2026-10-18): body face 0.400 / 0.570 / 0.360 inside the hex corner radius 0.5052 / 0.6131 / 0.5052, neck 0.304 / 0.304 / 0.2465, nothing outside the neck from the body face to the nut rear face (excess 0.000) - ASSUMED for every NPSM size (Q-ANGLED-NECKNPSM, settled from the Brennan STEPs 2026-10-18); past the swivel slot start the corner must lie inside the stem by 0.02 (slot test on what the corner reaches, N2); female NPTF port on the 45 deg leg (Q-NEW-ANGLEDFEMALE): the 5504 / 1502 forged female leg turned to the 135 deg axis - hex arm to 0.26 short of the port face, round collar of dia = the hex flats, tap drill from the port face (pocket), tapered helical thread over the port depth (Brennan 1504-06-06-FG / 5505-08-08-FG / 5503-16-16-FG STEPs: collar 0.26 at the flats dia on the 45 deg leg, the same end as on the axis legs); helical thread on the 45 deg leg (HelixThreadV, 2026-10-18): helix on the leg end face (circle centred on the leg axis), started in the Front Plane, right hand, into the part, tapered as on the axis legs; 60deg tooth profile on the Front Plane with its sides parallel / normal to the leg axis, swept along the helix - the thread of the axis legs (HelixThread) about the 135 deg axis; SolidWorks' Thread feature is not used there (an off-axis Thread feature crashed SolidWorks 2026-10-15); drawing-only thread, suppressed in the saved model and STEP; leg 2 port depth 0.940 = the row PORTDEPTH instead of MS51503 P1 1.14 (which does not fit the 1.19 leg): the port depth Brennan draws for -16: 0.940 (Brennan 5405-16-16, 5502-16-16-FG, 5503-16-16-FG STEPs); female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: tap drill = the row's TAPDRILL (end library: the per-size tap drill every built female pipe port carries, Q-TRANSFER-ENDLIB = yes 2026-10-08), tapered helix over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - where that does not fit the short 45 deg leg (P1 &gt;= leg - 0.05) over the row's PORTDEPTH = the port depth Brennan draws for that size (Q-ANGLED-P1, settled from the Brennan STEPs 2026-10-18; said per leg below); connecting drill to the axis crossing = the tap drill carried to the crossing (Brennan 1504-06-06-FG / 5503-16-16-FG / 5505-08-08-FG STEPs, OCP 2026-10-18: the drill runs from the bottom of the tapered port to the axis crossing and ends flat there; the other leg bore opens into it); the 1.79deg port cone and the 45deg mouth chamfer are NOT modelled; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>2026-10-18 (wave 3 adapters, staged, not shipped): NEW row - OMi sells this part (SKU dropped by the 2026-09-23 crawl; two-pass crawl 2026-10-16, tools/_out/adapters77_20261016/REPORT_77.md); Air-Way does not print this size; sizes from the Brennan TFA catalog p.22 alone, end details from the end library; marked DimSource BRENNAN | 2026-10-20: DataStatus MISSING -&gt; ASSUMED (Brennan catalog only; 1504 / 6807 SPEC exists since batch 17) | leg 1: the corner (radius 0.938) reaches past the swivel slot start (0.835) but stays inside the stem there (worst margin 0.1628 at 0.8353: corner 0.4272 off the axis vs 0.5900) - hidden in solid (slot test N2, 2026-10-18); leg 1: the corner (puck radius 0.938; the angled hex arm starts at 0.663 along this leg) stands 0.162 out of the neck past the swivel body face (0.640; 0.687 off the axis vs neck radius 0.525) - turned down to the neck from the body face to the nut rear face (0.680) by NECKTRIM1 / NECKFILL1, as on the Brennan 6502-12-12-FG STEP (NECK-6502, 2026-10-01)</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>1504-16-16-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1504-20-20-FG</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9048</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.195</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.08253</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.8141</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.6405</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.555</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.7775</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.84707</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.08696</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.80957</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0.9375</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.54077</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.54077</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>1.08203</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AZ7" t="n">
         <v>0.6</v>
       </c>
-      <c r="BE4" t="n">
+      <c r="BA7" t="n">
+        <v>1.6238</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BE7" t="n">
         <v>0.695</v>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>1504-20-20-FG</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>45 deg Female Pipe x Female NPSM Swivel Elbow, 1 1/4-11 1/2 NPSM (female swivel) x 1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="BH4" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>1504</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>1 1/4-11 1/2 NPSM (female swivel)</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>1 1/4-11 1/2 NPTF (female)</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; OMi answer 2026-10-18 (staged, not shipped): every size from OMi's drawing zip_b/1504-20-20-FG.pdf (07_RAW_EXTRACTS/omi_answers_20261018, sha256 a9d438ebfceb29dc...; a Brennan-format sheet OMi sent in answer to our 2026-10-09 size request; user 2026-10-18: "this is verified information, use it"); one source (OMi = Brennan data, evidence 2026-09-26) -&gt; ASSUMED; tap drill / thread majors from the end library (Q-TRANSFER-ENDLIB); end and body SHAPE from the Brennan 3D files (shape only, user 2026-10-08) | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; female NPSM SWIVEL end, sectioned on the Brennan 1404 STEPs (one per NPSM size -02/-04/-06/-08/-12/-16/-20/-24/-32): nut hex = Air-Way C(2) (must equal the Brennan nut, checked per row) over the measured hex length, skirt cone and lip to the measured nut rear face; nut thread = straight NPSM of that size, minor = the Brennan value (-08: 0.759 = ASME B1.20.1 NPSM internal minor 0.7594 min), helical 60deg thread 0.8P deep over the measured length, 45deg countersink and 45deg relief to the measured counterbore; body stem with the measured 30deg male cone, OD and tip radius, neck behind the nut, the forged hex arm ends at the measured body face behind the stem tip (Brennan 1404 straight body face - ASSUMED for the elbow forging); NUT FACE AT AIR-WAY W2 AND STEM TIP AT AIR-WAY M1/M (crossing to the stem tip) (user decision 2026-09-24: follow Air-Way - at -08 Air-Way W-L 0.33 vs Brennan 0.28, so the nut sits 0.05 further out than on the Brennan part); NUT AND BODY ARE ONE SOLID (Brennan STEPs are one solid too) - the nut/collar joint, the rear undercut under the nut lip, the slot at the collar, hex chamfers and fillets are NOT modelled; single manufacturer (Brennan); NPSM swivel neck turned clear of the forged corner as on 6502 (NECKTRIM1 revolve cut + NECKFILL1 ring back to the neck, in every configuration; no change where the corner stays inside the neck): Brennan 1503-08-08-FG / 1503-12-08-FG / 1504-06-06-FG STEPs (tools/measure/neck45.py 2026-10-18): body face 0.400 / 0.570 / 0.360 inside the hex corner radius 0.5052 / 0.6131 / 0.5052, neck 0.304 / 0.304 / 0.2465, nothing outside the neck from the body face to the nut rear face (excess 0.000) - ASSUMED for every NPSM size (Q-ANGLED-NECKNPSM, settled from the Brennan STEPs 2026-10-18); past the swivel slot start the corner must lie inside the stem by 0.02 (slot test on what the corner reaches, N2); female NPTF port on the 45 deg leg (Q-NEW-ANGLEDFEMALE): the 5504 / 1502 forged female leg turned to the 135 deg axis - hex arm to 0.26 short of the port face, round collar of dia = the hex flats, tap drill from the port face (pocket), tapered helical thread over the port depth (Brennan 1504-06-06-FG / 5505-08-08-FG / 5503-16-16-FG STEPs: collar 0.26 at the flats dia on the 45 deg leg, the same end as on the axis legs); helical thread on the 45 deg leg (HelixThreadV, 2026-10-18): helix on the leg end face (circle centred on the leg axis), started in the Front Plane, right hand, into the part, tapered as on the axis legs; 60deg tooth profile on the Front Plane with its sides parallel / normal to the leg axis, swept along the helix - the thread of the axis legs (HelixThread) about the 135 deg axis; SolidWorks' Thread feature is not used there (an off-axis Thread feature crashed SolidWorks 2026-10-15); drawing-only thread, suppressed in the saved model and STEP; female legs: the forged hex arm stops 0.26 short of the port face and the end is a ROUND COLLAR of dia = the hex flats - MEASURED on the Brennan 2502-06-04-FG, 5502-04-04/-08-08/-16-16-FG, 5504-08-08-FG and 5605-08-08-08-FG STEPs (collar 0.260 at every size and leg; single manufacturer); port-mouth 45deg chamfer and hex chamfers not modelled; female NPTF legs: tap drill = the row's TAPDRILL (end library: the per-size tap drill every built female pipe port carries, Q-TRANSFER-ENDLIB = yes 2026-10-08), tapered helix over MS51503 P1 max (Brennan 5405-08-08 STEP: 1/2 NPTF port drill depth 0.900 = MS51503 P1 max (VERIFIED -08 only)) - where that does not fit the short 45 deg leg (P1 &gt;= leg - 0.05) over the row's PORTDEPTH = the port depth Brennan draws for that size (Q-ANGLED-P1, settled from the Brennan STEPs 2026-10-18; said per leg below); connecting drill to the axis crossing = the tap drill carried to the crossing (Brennan 1504-06-06-FG / 5503-16-16-FG / 5505-08-08-FG STEPs, OCP 2026-10-18: the drill runs from the bottom of the tapered port to the axis crossing and ends flat there; the other leg bore opens into it); the 1.79deg port cone and the 45deg mouth chamfer are NOT modelled; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | OMi answer 2026-10-18 (staged, not shipped): was MISSING (no Air-Way row / non-forged Air-Way row only); now filled from OMi's own drawing; non-forged Air-Way row NOT used | VERIFIED by user decision 2026-10-18 (A23-1: OMi's own answer counts as verified) | DataStatus VERIFIED -&gt; ASSUMED: the NPSM swivel nut/stem geometry is single-source (Brennan 1404-08-08 STEP) | leg 2: female port thread length = MS51503 P1 1.16 (library) - the row has no measured PORTDEPTH@BORE; leg 1: the corner (radius 1.083) reaches past the swivel slot start (0.956) but stays inside the stem there (worst margin 0.2599 at 0.9559: corner 0.5081 off the axis vs 0.7680) - hidden in solid (slot test N2, 2026-10-18); leg 1: the corner (puck radius 1.083; the angled hex arm starts at 0.765 along this leg) stands 0.106 out of the neck past the swivel body face (0.730; 0.801 off the axis vs neck radius 0.695) - turned down to the neck from the body face to the nut rear face (0.770) by NECKTRIM1 / NECKFILL1, as on the Brennan 6502-12-12-FG STEP (NECK-6502, 2026-10-01)</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>1504-20-20-FG</t>
         </is>
